--- a/results/ahp/ahp_weights.xlsx
+++ b/results/ahp/ahp_weights.xlsx
@@ -470,25 +470,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.540625</v>
+        <v>0.5578920000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.253506</v>
+        <v>0.263345</v>
       </c>
       <c r="D2" t="n">
-        <v>0.117418</v>
+        <v>0.121873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.088451</v>
+        <v>0.05689</v>
       </c>
       <c r="F2" t="n">
-        <v>4.147126</v>
+        <v>4.118466</v>
       </c>
       <c r="G2" t="n">
-        <v>0.049042</v>
+        <v>0.039489</v>
       </c>
       <c r="H2" t="n">
-        <v>0.054491</v>
+        <v>0.043876</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -503,25 +503,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.643553</v>
+        <v>0.626362</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1943</v>
+        <v>0.222358</v>
       </c>
       <c r="D3" t="n">
-        <v>0.093108</v>
+        <v>0.102532</v>
       </c>
       <c r="E3" t="n">
-        <v>0.069039</v>
+        <v>0.048748</v>
       </c>
       <c r="F3" t="n">
-        <v>4.166007</v>
+        <v>4.128247</v>
       </c>
       <c r="G3" t="n">
-        <v>0.055336</v>
+        <v>0.042749</v>
       </c>
       <c r="H3" t="n">
-        <v>0.061484</v>
+        <v>0.047499</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.406194</v>
+        <v>0.420931</v>
       </c>
       <c r="C4" t="n">
-        <v>0.406194</v>
+        <v>0.420931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.105293</v>
+        <v>0.106408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.082319</v>
+        <v>0.05173</v>
       </c>
       <c r="F4" t="n">
-        <v>4.106729</v>
+        <v>4.074938</v>
       </c>
       <c r="G4" t="n">
-        <v>0.035576</v>
+        <v>0.024979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.039529</v>
+        <v>0.027755</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
